--- a/output/coefficients/standardized/standardized_PAL.xlsx
+++ b/output/coefficients/standardized/standardized_PAL.xlsx
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2223184151331574</v>
+        <v>0.2223</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007954534617253751</v>
+        <v>0.008</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>27.94863883688916</v>
+        <v>27.9486</v>
       </c>
       <c r="G2" t="n">
         <v>6.848253084229291e-172</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05791629399901178</v>
+        <v>0.0579</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003325955595044214</v>
+        <v>0.0033</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2254799177218793</v>
+        <v>0.2255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01294862191855697</v>
+        <v>0.0129</v>
       </c>
       <c r="F3" t="n">
-        <v>17.41342971785583</v>
+        <v>17.4134</v>
       </c>
       <c r="G3" t="n">
         <v>6.52548235122811e-68</v>
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.116495056224795</v>
+        <v>-0.1165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005260636528222098</v>
+        <v>0.0053</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2631166039349796</v>
+        <v>-0.2631</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01188171294729581</v>
+        <v>0.0119</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.14466929996512</v>
+        <v>-22.1447</v>
       </c>
       <c r="G4" t="n">
         <v>1.174196130163128e-108</v>
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005547012012503857</v>
+        <v>0.0055</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004839974841475091</v>
+        <v>0.0005</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1241219899536324</v>
+        <v>0.1241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01083010650229752</v>
+        <v>0.0108</v>
       </c>
       <c r="F5" t="n">
-        <v>11.4608281947459</v>
+        <v>11.4608</v>
       </c>
       <c r="G5" t="n">
         <v>2.07520829055946e-30</v>
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06248938180439636</v>
+        <v>0.0625</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00790846700924375</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1144776488886845</v>
+        <v>0.1145</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01448794472580711</v>
+        <v>0.0145</v>
       </c>
       <c r="F6" t="n">
-        <v>7.901579627424143</v>
+        <v>7.9016</v>
       </c>
       <c r="G6" t="n">
         <v>2.753908328349476e-15</v>
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07112519003058633</v>
+        <v>0.0711</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008784942602163932</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.122131774420529</v>
+        <v>0.1221</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0150849597410339</v>
+        <v>0.0151</v>
       </c>
       <c r="F7" t="n">
-        <v>8.096261210980089</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="G7" t="n">
         <v>5.667406196789904e-16</v>
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06742474315306365</v>
+        <v>0.0674</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008177551961045871</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09478414953304827</v>
+        <v>0.0948</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01149581402379914</v>
+        <v>0.0115</v>
       </c>
       <c r="F8" t="n">
-        <v>8.245101159154279</v>
+        <v>8.245100000000001</v>
       </c>
       <c r="G8" t="n">
         <v>1.650205533892556e-16</v>
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04473164934305855</v>
+        <v>0.0447</v>
       </c>
       <c r="C9" t="n">
-        <v>0.007941617831481491</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0553200161215196</v>
+        <v>0.0553</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009821467192035898</v>
+        <v>0.0098</v>
       </c>
       <c r="F9" t="n">
-        <v>5.632561310837335</v>
+        <v>5.6326</v>
       </c>
       <c r="G9" t="n">
         <v>1.775526925826283e-08</v>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1096184412738307</v>
+        <v>0.1096</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01039666413156494</v>
+        <v>0.0104</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1579829814346467</v>
+        <v>0.158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01498375617635603</v>
+        <v>0.015</v>
       </c>
       <c r="F10" t="n">
-        <v>10.54361667229607</v>
+        <v>10.5436</v>
       </c>
       <c r="G10" t="n">
         <v>5.436701966806563e-26</v>
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06243000601204574</v>
+        <v>0.0624</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008170948514893544</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08835295873157133</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01156378996335334</v>
+        <v>0.0116</v>
       </c>
       <c r="F11" t="n">
-        <v>7.640484565317214</v>
+        <v>7.6405</v>
       </c>
       <c r="G11" t="n">
         <v>2.16405738727976e-14</v>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07535407603663703</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01029754399503835</v>
+        <v>0.0103</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08287901105849291</v>
+        <v>0.0829</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01132586725932588</v>
+        <v>0.0113</v>
       </c>
       <c r="F12" t="n">
-        <v>7.317674590460094</v>
+        <v>7.3177</v>
       </c>
       <c r="G12" t="n">
         <v>2.523047702038281e-13</v>
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05641304178896852</v>
+        <v>0.0564</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008559940075658249</v>
+        <v>0.0086</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06676359191489156</v>
+        <v>0.0668</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01013050046414848</v>
+        <v>0.0101</v>
       </c>
       <c r="F13" t="n">
-        <v>6.590354756032615</v>
+        <v>6.5904</v>
       </c>
       <c r="G13" t="n">
         <v>4.387768640253819e-11</v>
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03244946472807977</v>
+        <v>0.0324</v>
       </c>
       <c r="C14" t="n">
-        <v>0.009013322180690205</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03223605229533273</v>
+        <v>0.0322</v>
       </c>
       <c r="E14" t="n">
-        <v>0.008954043698600193</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.600166961478227</v>
+        <v>3.6002</v>
       </c>
       <c r="G14" t="n">
         <v>0.0003180129136090101</v>
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01060733010991921</v>
+        <v>0.0106</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008376711420939504</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.009314668233806809</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007355883805617339</v>
+        <v>0.0074</v>
       </c>
       <c r="F15" t="n">
-        <v>1.266288114379083</v>
+        <v>1.2663</v>
       </c>
       <c r="G15" t="n">
         <v>0.2054099506572642</v>
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02730608243144142</v>
+        <v>0.0273</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008604047380252196</v>
+        <v>0.0086</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02447944447961795</v>
+        <v>0.0245</v>
       </c>
       <c r="E16" t="n">
-        <v>0.007713384029866039</v>
+        <v>0.0077</v>
       </c>
       <c r="F16" t="n">
-        <v>3.173632271495121</v>
+        <v>3.1736</v>
       </c>
       <c r="G16" t="n">
         <v>0.001505442893215186</v>
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08791933960749647</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01732298898188624</v>
+        <v>0.0173</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05954487786088768</v>
+        <v>0.0595</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01173229084427709</v>
+        <v>0.0117</v>
       </c>
       <c r="F17" t="n">
-        <v>5.075298477614296</v>
+        <v>5.0753</v>
       </c>
       <c r="G17" t="n">
         <v>3.868882024923099e-07</v>
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0542443387540471</v>
+        <v>0.0542</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02308261176152301</v>
+        <v>0.0231</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02288343080118621</v>
+        <v>0.0229</v>
       </c>
       <c r="E18" t="n">
-        <v>0.009737594025257607</v>
+        <v>0.0097</v>
       </c>
       <c r="F18" t="n">
-        <v>2.350008712812488</v>
+        <v>2.35</v>
       </c>
       <c r="G18" t="n">
         <v>0.01877297163093312</v>
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.04678883689359144</v>
+        <v>0.0468</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0234889149538298</v>
+        <v>0.0235</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01398388554548594</v>
+        <v>0.014</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007020185157605366</v>
+        <v>0.007</v>
       </c>
       <c r="F19" t="n">
-        <v>1.991953948726893</v>
+        <v>1.992</v>
       </c>
       <c r="G19" t="n">
         <v>0.046376110863128</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1021619368057968</v>
+        <v>-0.1022</v>
       </c>
       <c r="C20" t="n">
-        <v>0.004974944117678012</v>
+        <v>0.005</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1996522773328006</v>
+        <v>-0.1997</v>
       </c>
       <c r="E20" t="n">
-        <v>0.009722397144701314</v>
+        <v>0.0097</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.53529333983344</v>
+        <v>-20.5353</v>
       </c>
       <c r="G20" t="n">
         <v>1.041834936009393e-93</v>
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1019076787667108</v>
+        <v>-0.1019</v>
       </c>
       <c r="C21" t="n">
-        <v>0.005449899312128422</v>
+        <v>0.0054</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1739300660131559</v>
+        <v>-0.1739</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00930156940669314</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.69900211549255</v>
+        <v>-18.699</v>
       </c>
       <c r="G21" t="n">
         <v>5.043982096799466e-78</v>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1214543165837861</v>
+        <v>-0.1215</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007254663836294343</v>
+        <v>0.0073</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1595870900986786</v>
+        <v>-0.1596</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00953239640914408</v>
+        <v>0.0095</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.74154989458816</v>
+        <v>-16.7415</v>
       </c>
       <c r="G22" t="n">
         <v>6.526643723517673e-63</v>
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07031173417326558</v>
+        <v>-0.0703</v>
       </c>
       <c r="C23" t="n">
-        <v>0.005972164892425402</v>
+        <v>0.006</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.137291866324466</v>
+        <v>-0.1373</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01166134890170718</v>
+        <v>0.0117</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.77324059863838</v>
+        <v>-11.7732</v>
       </c>
       <c r="G23" t="n">
         <v>5.362426103971977e-32</v>
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1013615948052559</v>
+        <v>-0.1014</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007673153890562856</v>
+        <v>0.0077</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1150911202181795</v>
+        <v>-0.1151</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00871248995803655</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.20989989916918</v>
+        <v>-13.2099</v>
       </c>
       <c r="G24" t="n">
         <v>7.692666028543185e-40</v>

--- a/output/coefficients/standardized/standardized_PAL.xlsx
+++ b/output/coefficients/standardized/standardized_PAL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2223</v>
+        <v>0.2365</v>
       </c>
       <c r="C2" t="n">
         <v>0.008</v>
@@ -468,10 +468,10 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>27.9486</v>
+        <v>29.5134</v>
       </c>
       <c r="G2" t="n">
-        <v>6.848253084229291e-172</v>
+        <v>1.935312902244293e-191</v>
       </c>
     </row>
     <row r="3">
@@ -481,22 +481,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0579</v>
+        <v>0.0561</v>
       </c>
       <c r="C3" t="n">
         <v>0.0033</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2255</v>
+        <v>0.2184</v>
       </c>
       <c r="E3" t="n">
         <v>0.0129</v>
       </c>
       <c r="F3" t="n">
-        <v>17.4134</v>
+        <v>16.9424</v>
       </c>
       <c r="G3" t="n">
-        <v>6.52548235122811e-68</v>
+        <v>2.188213823860349e-64</v>
       </c>
     </row>
     <row r="4">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1165</v>
+        <v>-0.1091</v>
       </c>
       <c r="C4" t="n">
         <v>0.0053</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2631</v>
+        <v>-0.2465</v>
       </c>
       <c r="E4" t="n">
         <v>0.0119</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.1447</v>
+        <v>-20.7673</v>
       </c>
       <c r="G4" t="n">
-        <v>1.174196130163128e-108</v>
+        <v>8.561217405919038e-96</v>
       </c>
     </row>
     <row r="5">
@@ -531,22 +531,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0055</v>
+        <v>0.005</v>
       </c>
       <c r="C5" t="n">
         <v>0.0005</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1241</v>
+        <v>0.1108</v>
       </c>
       <c r="E5" t="n">
         <v>0.0108</v>
       </c>
       <c r="F5" t="n">
-        <v>11.4608</v>
+        <v>10.3036</v>
       </c>
       <c r="G5" t="n">
-        <v>2.07520829055946e-30</v>
+        <v>6.78429140847246e-25</v>
       </c>
     </row>
     <row r="6">
@@ -556,22 +556,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0625</v>
+        <v>0.0562</v>
       </c>
       <c r="C6" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1145</v>
+        <v>0.1029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0145</v>
+        <v>0.0144</v>
       </c>
       <c r="F6" t="n">
-        <v>7.9016</v>
+        <v>7.1263</v>
       </c>
       <c r="G6" t="n">
-        <v>2.753908328349476e-15</v>
+        <v>1.031254404489016e-12</v>
       </c>
     </row>
     <row r="7">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0711</v>
+        <v>0.0594</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1221</v>
+        <v>0.102</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0151</v>
+        <v>0.015</v>
       </c>
       <c r="F7" t="n">
-        <v>8.096299999999999</v>
+        <v>6.8066</v>
       </c>
       <c r="G7" t="n">
-        <v>5.667406196789904e-16</v>
+        <v>9.990440825400547e-12</v>
       </c>
     </row>
     <row r="8">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0674</v>
+        <v>0.0641</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0948</v>
+        <v>0.0901</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="F8" t="n">
-        <v>8.245100000000001</v>
+        <v>7.9224</v>
       </c>
       <c r="G8" t="n">
-        <v>1.650205533892556e-16</v>
+        <v>2.329922375313903e-15</v>
       </c>
     </row>
     <row r="9">
@@ -631,22 +631,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0447</v>
+        <v>0.0453</v>
       </c>
       <c r="C9" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0553</v>
+        <v>0.056</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0098</v>
+        <v>0.0097</v>
       </c>
       <c r="F9" t="n">
-        <v>5.6326</v>
+        <v>5.755</v>
       </c>
       <c r="G9" t="n">
-        <v>1.775526925826283e-08</v>
+        <v>8.664252843529594e-09</v>
       </c>
     </row>
     <row r="10">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1096</v>
+        <v>0.1042</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0104</v>
+        <v>0.0103</v>
       </c>
       <c r="D10" t="n">
-        <v>0.158</v>
+        <v>0.1501</v>
       </c>
       <c r="E10" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
       <c r="F10" t="n">
-        <v>10.5436</v>
+        <v>10.1623</v>
       </c>
       <c r="G10" t="n">
-        <v>5.436701966806563e-26</v>
+        <v>2.919873706899104e-24</v>
       </c>
     </row>
     <row r="11">
@@ -681,22 +681,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0624</v>
+        <v>0.0616</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0872</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0116</v>
+        <v>0.0115</v>
       </c>
       <c r="F11" t="n">
-        <v>7.6405</v>
+        <v>7.575</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16405738727976e-14</v>
+        <v>3.592642487954667e-14</v>
       </c>
     </row>
     <row r="12">
@@ -706,22 +706,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0103</v>
+        <v>0.0102</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0829</v>
+        <v>0.075</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0113</v>
+        <v>0.0112</v>
       </c>
       <c r="F12" t="n">
-        <v>7.3177</v>
+        <v>6.7122</v>
       </c>
       <c r="G12" t="n">
-        <v>2.523047702038281e-13</v>
+        <v>1.917366524943948e-11</v>
       </c>
     </row>
     <row r="13">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0564</v>
+        <v>0.0504</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0086</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0668</v>
+        <v>0.0596</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0101</v>
+        <v>0.01</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5904</v>
+        <v>5.9328</v>
       </c>
       <c r="G13" t="n">
-        <v>4.387768640253819e-11</v>
+        <v>2.978592861436064e-09</v>
       </c>
     </row>
     <row r="14">
@@ -756,22 +756,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0324</v>
+        <v>0.0321</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0322</v>
+        <v>0.0319</v>
       </c>
       <c r="E14" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6002</v>
+        <v>3.621</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0003180129136090101</v>
+        <v>0.0002934666453694434</v>
       </c>
     </row>
     <row r="15">
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0106</v>
+        <v>0.0067</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="D15" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0074</v>
+        <v>0.0073</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2663</v>
+        <v>0.8081</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2054099506572642</v>
+        <v>0.4190591852696735</v>
       </c>
     </row>
     <row r="16">
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0273</v>
+        <v>0.0323</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0086</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0245</v>
+        <v>0.029</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0077</v>
+        <v>0.0078</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1736</v>
+        <v>3.7023</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001505442893215186</v>
+        <v>0.000213681386164429</v>
       </c>
     </row>
     <row r="17">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0595</v>
+        <v>0.0523</v>
       </c>
       <c r="E17" t="n">
         <v>0.0117</v>
       </c>
       <c r="F17" t="n">
-        <v>5.0753</v>
+        <v>4.4864</v>
       </c>
       <c r="G17" t="n">
-        <v>3.868882024923099e-07</v>
+        <v>7.244521904004026e-06</v>
       </c>
     </row>
     <row r="18">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0542</v>
+        <v>0.0414</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0231</v>
+        <v>0.0227</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0229</v>
+        <v>0.0175</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.35</v>
+        <v>1.8233</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01877297163093312</v>
+        <v>0.06825282942830668</v>
       </c>
     </row>
     <row r="19">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0468</v>
+        <v>0.0309</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0235</v>
+        <v>0.0236</v>
       </c>
       <c r="D19" t="n">
-        <v>0.014</v>
+        <v>0.0092</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.0071</v>
       </c>
       <c r="F19" t="n">
-        <v>1.992</v>
+        <v>1.307</v>
       </c>
       <c r="G19" t="n">
-        <v>0.046376110863128</v>
+        <v>0.1912086943180784</v>
       </c>
     </row>
     <row r="20">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1022</v>
+        <v>-0.0955</v>
       </c>
       <c r="C20" t="n">
-        <v>0.005</v>
+        <v>0.0049</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1997</v>
+        <v>-0.1867</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.5353</v>
+        <v>-19.4143</v>
       </c>
       <c r="G20" t="n">
-        <v>1.041834936009393e-93</v>
+        <v>5.839484225313443e-84</v>
       </c>
     </row>
     <row r="21">
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1019</v>
+        <v>-0.0973</v>
       </c>
       <c r="C21" t="n">
         <v>0.0054</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1739</v>
+        <v>-0.166</v>
       </c>
       <c r="E21" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0092</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.699</v>
+        <v>-18.0107</v>
       </c>
       <c r="G21" t="n">
-        <v>5.043982096799466e-78</v>
+        <v>1.605448232048225e-72</v>
       </c>
     </row>
     <row r="22">
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1215</v>
+        <v>-0.1178</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0073</v>
+        <v>0.0072</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1596</v>
+        <v>-0.1548</v>
       </c>
       <c r="E22" t="n">
         <v>0.0095</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.7415</v>
+        <v>-16.3596</v>
       </c>
       <c r="G22" t="n">
-        <v>6.526643723517673e-63</v>
+        <v>3.714453782580163e-60</v>
       </c>
     </row>
     <row r="23">
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0703</v>
+        <v>-0.0711</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006</v>
+        <v>0.0059</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1373</v>
+        <v>-0.1389</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0117</v>
+        <v>0.0116</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.7732</v>
+        <v>-11.9933</v>
       </c>
       <c r="G23" t="n">
-        <v>5.362426103971977e-32</v>
+        <v>3.851077963661381e-33</v>
       </c>
     </row>
     <row r="24">
@@ -1006,22 +1006,97 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1014</v>
+        <v>-0.1016</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1151</v>
+        <v>-0.1154</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0086</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.2099</v>
+        <v>-13.3482</v>
       </c>
       <c r="G24" t="n">
-        <v>7.692666028543185e-40</v>
+        <v>1.214058286056416e-40</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>d_aa</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.0864</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-12.4908</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.380030162345431e-36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>d_indie</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.0306</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-6.6292</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.374381682041112e-11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>d_unknown</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.0586</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-15.2322</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.162640598758015e-52</v>
       </c>
     </row>
   </sheetData>
